--- a/Dashboard_RH/data/SOCIAL.xlsx
+++ b/Dashboard_RH/data/SOCIAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcelormittal-my.sharepoint.com/personal/fallah_sonasid_ma/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcelormittal-my.sharepoint.com/personal/labiad_sonasid_ma/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{B1814551-7CF3-42A3-B22B-5B29B592D6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899E9A15-B206-4AD0-B3F4-49076697E557}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{B3A231A6-DD9C-4D6B-AC5B-E43D038C682A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1EAA272-2EB3-4ED1-94CA-60A5948E43D1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CA46B2A-96C9-432D-9D44-1AD5E034063C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1CA46B2A-96C9-432D-9D44-1AD5E034063C}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="49">
   <si>
     <t xml:space="preserve">Actions </t>
   </si>
@@ -191,6 +191,60 @@
   <si>
     <t>Organisation d’une semaine de sensibilisation à la protection de l’environnement, avec la participation d’étudiants universitaires: conférences, nettoyage de plage et activités de sensibilisation.</t>
   </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>DEPISTAGE PULMONAIRE</t>
+  </si>
+  <si>
+    <t>Siege, PFC , Jorf</t>
+  </si>
+  <si>
+    <t>JOURNEE DE LA FEMME</t>
+  </si>
+  <si>
+    <t>Fevrier / Avril 2026</t>
+  </si>
+  <si>
+    <t>Casablanca , Jorf , Nador</t>
+  </si>
+  <si>
+    <t>CIRCONCISION</t>
+  </si>
+  <si>
+    <t>Jorf, Nador</t>
+  </si>
+  <si>
+    <t>CENTRE AERE</t>
+  </si>
+  <si>
+    <t>Siege et PFC</t>
+  </si>
+  <si>
+    <t>Family Day</t>
+  </si>
+  <si>
+    <t>Achoura</t>
+  </si>
+  <si>
+    <t>Excursion</t>
+  </si>
+  <si>
+    <t>RENTREE SCOLAIRE</t>
+  </si>
+  <si>
+    <t>Septembre 2026</t>
+  </si>
+  <si>
+    <t>Type Action</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Sociétales </t>
+  </si>
 </sst>
 </file>
 
@@ -206,12 +260,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -240,8 +288,16 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,8 +310,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -278,34 +346,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -314,6 +437,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -642,202 +771,415 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA88646-7528-4C35-83C7-ACBB40CC29AD}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.36328125" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.08984375" customWidth="1"/>
-    <col min="5" max="5" width="26.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="118.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="118.81640625" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="30.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="8">
         <v>700</v>
       </c>
-      <c r="D2" s="6">
+      <c r="E2" s="9">
         <v>300000</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="8">
         <v>1500</v>
       </c>
-      <c r="D3" s="6">
+      <c r="E3" s="9">
         <v>414756</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="76" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="8">
         <v>40</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="9">
         <v>87072</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="8">
         <v>16</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="9">
         <v>296736</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="5" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="8">
         <v>150</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="9">
         <v>60000</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="5" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="8">
         <v>140</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="9">
         <v>222150</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="5" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="9">
         <v>58080</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="5" customFormat="1" ht="95" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="8">
         <v>580</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="9">
         <v>767676</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
+    <row r="10" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="12">
+        <v>617</v>
+      </c>
+      <c r="E10" s="13">
+        <v>42390</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="12">
+        <v>68</v>
+      </c>
+      <c r="E11" s="13">
+        <v>95200</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="12">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13">
+        <v>13100</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="12">
+        <v>19</v>
+      </c>
+      <c r="E13" s="13">
+        <v>40000</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="12">
+        <v>113</v>
+      </c>
+      <c r="E14" s="13">
+        <v>639730</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="12">
+        <v>767</v>
+      </c>
+      <c r="E15" s="15">
+        <v>266700</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="18">
+        <v>288</v>
+      </c>
+      <c r="E16" s="15">
+        <v>323643.84000000003</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="4">
+        <v>636</v>
+      </c>
+      <c r="E17" s="5">
+        <v>311350</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
